--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.71845602326703</v>
+        <v>1.741749103780892</v>
       </c>
       <c r="D2" t="n">
-        <v>10.30268581118091</v>
+        <v>1.674186444316899</v>
       </c>
       <c r="E2" t="n">
-        <v>8.985877830118699</v>
+        <v>1.460205147394289</v>
       </c>
       <c r="F2" t="n">
-        <v>9.858568735549646</v>
+        <v>1.602017419526818</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.88535488737758</v>
+        <v>5.343870169198857</v>
       </c>
       <c r="D3" t="n">
-        <v>12.74762029804334</v>
+        <v>2.071488298432043</v>
       </c>
       <c r="E3" t="n">
-        <v>8.985877830118699</v>
+        <v>1.460205147394289</v>
       </c>
       <c r="F3" t="n">
-        <v>9.858568735549646</v>
+        <v>1.602017419526818</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.29358955500368</v>
+        <v>2.160208302688098</v>
       </c>
       <c r="D4" t="n">
-        <v>27.48736006530465</v>
+        <v>4.466696010612005</v>
       </c>
       <c r="E4" t="n">
-        <v>8.985877830118699</v>
+        <v>1.460205147394289</v>
       </c>
       <c r="F4" t="n">
-        <v>9.858568735549646</v>
+        <v>1.602017419526818</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.867245645354598</v>
+        <v>1.115927417370122</v>
       </c>
       <c r="D5" t="n">
-        <v>29.66343712577103</v>
+        <v>4.820308532937792</v>
       </c>
       <c r="E5" t="n">
-        <v>8.985877830118699</v>
+        <v>1.460205147394289</v>
       </c>
       <c r="F5" t="n">
-        <v>9.858568735549646</v>
+        <v>1.602017419526818</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8902485820707</v>
+        <v>2.58216539458649</v>
       </c>
       <c r="D6" t="n">
-        <v>35.45682907981284</v>
+        <v>5.761734725469587</v>
       </c>
       <c r="E6" t="n">
-        <v>8.985877830118699</v>
+        <v>1.460205147394289</v>
       </c>
       <c r="F6" t="n">
-        <v>9.858568735549646</v>
+        <v>1.602017419526818</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
